--- a/excel/11Vlookup函数.xlsx
+++ b/excel/11Vlookup函数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Desktop/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FB54B5-F843-DC46-AE74-FDDF6387B6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEBD78F-135C-ED4B-8CEF-3819A3699FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{ED6C2478-89A9-BA46-AFF4-9469C43EBEBE}"/>
   </bookViews>
@@ -3121,6 +3121,19 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3162,19 +3175,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3279,7 +3279,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="PIC" spid="_x0000_s3162"/>
+                  <a14:cameraTool cellRange="PIC" spid="_x0000_s3164"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -4291,25 +4291,25 @@
       <c r="B63" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="C63" s="73"/>
-      <c r="D63" s="73"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59"/>
     </row>
     <row r="64" spans="1:9">
       <c r="B64" s="50"/>
       <c r="C64" s="50" t="s">
         <v>717</v>
       </c>
-      <c r="D64" s="73"/>
+      <c r="D64" s="59"/>
     </row>
     <row r="65" spans="2:4">
-      <c r="B65" s="73"/>
+      <c r="B65" s="59"/>
       <c r="C65" s="50" t="s">
         <v>709</v>
       </c>
       <c r="D65" s="50"/>
     </row>
     <row r="66" spans="2:4">
-      <c r="B66" s="73"/>
+      <c r="B66" s="59"/>
       <c r="C66" s="50" t="s">
         <v>674</v>
       </c>
@@ -4318,7 +4318,7 @@
       </c>
     </row>
     <row r="67" spans="2:4">
-      <c r="B67" s="73"/>
+      <c r="B67" s="59"/>
       <c r="C67" s="50" t="s">
         <v>677</v>
       </c>
@@ -4327,7 +4327,7 @@
       </c>
     </row>
     <row r="68" spans="2:4">
-      <c r="B68" s="73"/>
+      <c r="B68" s="59"/>
       <c r="C68" s="50" t="s">
         <v>679</v>
       </c>
@@ -4336,7 +4336,7 @@
       </c>
     </row>
     <row r="69" spans="2:4">
-      <c r="B69" s="73"/>
+      <c r="B69" s="59"/>
       <c r="C69" s="50" t="s">
         <v>681</v>
       </c>
@@ -4345,7 +4345,7 @@
       </c>
     </row>
     <row r="70" spans="2:4">
-      <c r="B70" s="73"/>
+      <c r="B70" s="59"/>
       <c r="C70" s="50" t="s">
         <v>713</v>
       </c>
@@ -4354,7 +4354,7 @@
       </c>
     </row>
     <row r="71" spans="2:4">
-      <c r="B71" s="73"/>
+      <c r="B71" s="59"/>
       <c r="C71" s="50" t="s">
         <v>714</v>
       </c>
@@ -4389,14 +4389,14 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="32"/>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="60" t="s">
         <v>662</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="57"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="62"/>
       <c r="H1" s="49">
         <v>2</v>
       </c>
@@ -4410,8 +4410,8 @@
         <f>INDEX(数据源!A:A,H1)</f>
         <v>AABBCCD</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="59"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="64"/>
       <c r="F2" s="36"/>
       <c r="G2" s="37"/>
     </row>
@@ -4466,8 +4466,8 @@
       <c r="A6" s="38"/>
       <c r="B6" s="39"/>
       <c r="C6" s="39"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
       <c r="F6" s="41"/>
       <c r="G6" s="43"/>
     </row>
@@ -4480,8 +4480,8 @@
         <f>INDEX(数据源!I:I,H1)</f>
         <v>中国</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
       <c r="F7" s="41"/>
       <c r="G7" s="43"/>
       <c r="I7" t="e" vm="1">
@@ -4498,8 +4498,8 @@
         <f>INDEX(数据源!H:H,H1)</f>
         <v>343567</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
       <c r="F8" s="41"/>
       <c r="G8" s="43"/>
     </row>
@@ -4512,8 +4512,8 @@
         <f>INDEX(数据源!K:K,H1)</f>
         <v>(030) 30765452</v>
       </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
       <c r="F9" s="41"/>
       <c r="G9" s="43"/>
     </row>
@@ -4521,8 +4521,8 @@
       <c r="A10" s="38"/>
       <c r="B10" s="39"/>
       <c r="C10" s="39"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
       <c r="F10" s="41"/>
       <c r="G10" s="43"/>
     </row>
@@ -4531,15 +4531,15 @@
       <c r="B11" s="34" t="s">
         <v>671</v>
       </c>
-      <c r="C11" s="60" t="str">
+      <c r="C11" s="65" t="str">
         <f>INDEX(数据源!D:D,H1)</f>
         <v>销售代表</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="66">
         <f>INDEX(数据源!L:L,2)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="62">
+      <c r="E11" s="67">
         <f>INDEX(数据源!M:M,2)</f>
         <v>0</v>
       </c>
@@ -4551,15 +4551,15 @@
       <c r="B12" s="34" t="s">
         <v>672</v>
       </c>
-      <c r="C12" s="60" t="str">
+      <c r="C12" s="65" t="str">
         <f>INDEX(数据源!C:C,H1)</f>
         <v>刘小姐</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="66">
         <f>INDEX(数据源!L:L,2)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="62">
+      <c r="E12" s="67">
         <f>INDEX(数据源!M:M,2)</f>
         <v>0</v>
       </c>
@@ -4571,15 +4571,15 @@
       <c r="B13" s="34" t="s">
         <v>669</v>
       </c>
-      <c r="C13" s="63" t="str">
+      <c r="C13" s="68" t="str">
         <f>INDEX(数据源!J:J,H1)</f>
         <v>(030) 30074321</v>
       </c>
-      <c r="D13" s="64">
+      <c r="D13" s="69">
         <f>INDEX(数据源!L:L,2)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="65">
+      <c r="E13" s="70">
         <f>INDEX(数据源!M:M,2)</f>
         <v>0</v>
       </c>
@@ -4725,43 +4725,43 @@
       <c r="E1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="69" t="s">
+      <c r="G1" s="55" t="s">
         <v>718</v>
       </c>
-      <c r="H1" s="69" t="s">
+      <c r="H1" s="55" t="s">
         <v>719</v>
       </c>
-      <c r="I1" s="69" t="s">
+      <c r="I1" s="55" t="s">
         <v>720</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="J1" s="55" t="s">
         <v>721</v>
       </c>
-      <c r="K1" s="69" t="s">
+      <c r="K1" s="55" t="s">
         <v>722</v>
       </c>
-      <c r="L1" s="69" t="s">
+      <c r="L1" s="55" t="s">
         <v>723</v>
       </c>
-      <c r="M1" s="69" t="s">
+      <c r="M1" s="55" t="s">
         <v>724</v>
       </c>
-      <c r="N1" s="69" t="s">
+      <c r="N1" s="55" t="s">
         <v>725</v>
       </c>
-      <c r="O1" s="69" t="s">
+      <c r="O1" s="55" t="s">
         <v>726</v>
       </c>
-      <c r="P1" s="69" t="s">
+      <c r="P1" s="55" t="s">
         <v>727</v>
       </c>
-      <c r="Q1" s="69" t="s">
+      <c r="Q1" s="55" t="s">
         <v>728</v>
       </c>
-      <c r="R1" s="69" t="s">
+      <c r="R1" s="55" t="s">
         <v>729</v>
       </c>
-      <c r="S1" s="69" t="s">
+      <c r="S1" s="55" t="s">
         <v>730</v>
       </c>
     </row>
@@ -4794,31 +4794,31 @@
       <c r="J2">
         <v>302</v>
       </c>
-      <c r="K2" s="70">
+      <c r="K2" s="56">
         <v>54</v>
       </c>
-      <c r="L2" s="70">
+      <c r="L2" s="56">
         <v>59</v>
       </c>
-      <c r="M2" s="70">
+      <c r="M2" s="56">
         <v>185</v>
       </c>
-      <c r="N2" s="70">
+      <c r="N2" s="56">
         <v>261</v>
       </c>
-      <c r="O2" s="70">
+      <c r="O2" s="56">
         <v>160</v>
       </c>
-      <c r="P2" s="70">
+      <c r="P2" s="56">
         <v>158</v>
       </c>
-      <c r="Q2" s="70">
+      <c r="Q2" s="56">
         <v>158</v>
       </c>
-      <c r="R2" s="70">
+      <c r="R2" s="56">
         <v>178</v>
       </c>
-      <c r="S2" s="70">
+      <c r="S2" s="56">
         <v>242</v>
       </c>
     </row>
@@ -4851,31 +4851,31 @@
       <c r="J3">
         <v>305</v>
       </c>
-      <c r="K3" s="70">
+      <c r="K3" s="56">
         <v>230</v>
       </c>
-      <c r="L3" s="70">
+      <c r="L3" s="56">
         <v>237</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="56">
         <v>253</v>
       </c>
-      <c r="N3" s="70">
+      <c r="N3" s="56">
         <v>133</v>
       </c>
-      <c r="O3" s="70">
+      <c r="O3" s="56">
         <v>256</v>
       </c>
-      <c r="P3" s="70">
+      <c r="P3" s="56">
         <v>200</v>
       </c>
-      <c r="Q3" s="70">
+      <c r="Q3" s="56">
         <v>263</v>
       </c>
-      <c r="R3" s="70">
+      <c r="R3" s="56">
         <v>353</v>
       </c>
-      <c r="S3" s="70">
+      <c r="S3" s="56">
         <v>643</v>
       </c>
     </row>
@@ -4908,31 +4908,31 @@
       <c r="J4">
         <v>295</v>
       </c>
-      <c r="K4" s="70">
+      <c r="K4" s="56">
         <v>167</v>
       </c>
-      <c r="L4" s="70">
+      <c r="L4" s="56">
         <v>100</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="56">
         <v>49</v>
       </c>
-      <c r="N4" s="70">
+      <c r="N4" s="56">
         <v>185</v>
       </c>
-      <c r="O4" s="70">
+      <c r="O4" s="56">
         <v>88</v>
       </c>
-      <c r="P4" s="71">
+      <c r="P4" s="57">
         <v>208</v>
       </c>
-      <c r="Q4" s="70">
+      <c r="Q4" s="56">
         <v>296</v>
       </c>
-      <c r="R4" s="70">
+      <c r="R4" s="56">
         <v>157</v>
       </c>
-      <c r="S4" s="70">
+      <c r="S4" s="56">
         <v>256</v>
       </c>
     </row>
@@ -4965,31 +4965,31 @@
       <c r="J5">
         <v>210</v>
       </c>
-      <c r="K5" s="70">
+      <c r="K5" s="56">
         <v>70</v>
       </c>
-      <c r="L5" s="70">
+      <c r="L5" s="56">
         <v>105</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="56">
         <v>162</v>
       </c>
-      <c r="N5" s="70">
+      <c r="N5" s="56">
         <v>122</v>
       </c>
-      <c r="O5" s="70">
+      <c r="O5" s="56">
         <v>315</v>
       </c>
-      <c r="P5" s="70">
+      <c r="P5" s="56">
         <v>174</v>
       </c>
-      <c r="Q5" s="70">
+      <c r="Q5" s="56">
         <v>159</v>
       </c>
-      <c r="R5" s="70">
+      <c r="R5" s="56">
         <v>236</v>
       </c>
-      <c r="S5" s="70">
+      <c r="S5" s="56">
         <v>223</v>
       </c>
     </row>
@@ -5022,31 +5022,31 @@
       <c r="J6">
         <v>262</v>
       </c>
-      <c r="K6" s="70">
+      <c r="K6" s="56">
         <v>119</v>
       </c>
-      <c r="L6" s="70">
+      <c r="L6" s="56">
         <v>42</v>
       </c>
-      <c r="M6" s="70">
+      <c r="M6" s="56">
         <v>195</v>
       </c>
-      <c r="N6" s="70">
+      <c r="N6" s="56">
         <v>224</v>
       </c>
-      <c r="O6" s="70">
+      <c r="O6" s="56">
         <v>230</v>
       </c>
-      <c r="P6" s="70">
+      <c r="P6" s="56">
         <v>246</v>
       </c>
-      <c r="Q6" s="70">
+      <c r="Q6" s="56">
         <v>378</v>
       </c>
-      <c r="R6" s="70">
+      <c r="R6" s="56">
         <v>337</v>
       </c>
-      <c r="S6" s="70">
+      <c r="S6" s="56">
         <v>340</v>
       </c>
     </row>
@@ -5079,31 +5079,31 @@
       <c r="J7">
         <v>340</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="56">
         <v>30</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="56">
         <v>59</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="56">
         <v>169</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="56">
         <v>228</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="56">
         <v>213</v>
       </c>
-      <c r="P7" s="70">
+      <c r="P7" s="56">
         <v>230</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="56">
         <v>97</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="56">
         <v>139</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="56">
         <v>320</v>
       </c>
     </row>
@@ -5136,47 +5136,47 @@
       <c r="J8">
         <v>279</v>
       </c>
-      <c r="K8" s="70">
+      <c r="K8" s="56">
         <v>50</v>
       </c>
-      <c r="L8" s="70">
+      <c r="L8" s="56">
         <v>12</v>
       </c>
-      <c r="M8" s="70">
+      <c r="M8" s="56">
         <v>327</v>
       </c>
-      <c r="N8" s="70">
+      <c r="N8" s="56">
         <v>122</v>
       </c>
-      <c r="O8" s="70">
+      <c r="O8" s="56">
         <v>121</v>
       </c>
-      <c r="P8" s="70">
+      <c r="P8" s="56">
         <v>39</v>
       </c>
-      <c r="Q8" s="70">
+      <c r="Q8" s="56">
         <v>168</v>
       </c>
-      <c r="R8" s="70">
+      <c r="R8" s="56">
         <v>227</v>
       </c>
-      <c r="S8" s="70">
+      <c r="S8" s="56">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="58" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="69" t="s">
+      <c r="A13" s="55" t="s">
         <v>718</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="55" t="s">
         <v>738</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="55" t="s">
         <v>739</v>
       </c>
     </row>
